--- a/results/reliability_eval/reliability_eval_09-03-1/Llama-3-8B_P127_neg1_sample_15_tokens_0.1_temp_direct_answer_scores_09-03-1.xlsx
+++ b/results/reliability_eval/reliability_eval_09-03-1/Llama-3-8B_P127_neg1_sample_15_tokens_0.1_temp_direct_answer_scores_09-03-1.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5787172809428369</v>
+        <v>0.5599993183393231</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7839669903453134</v>
+        <v>0.7567206141457</v>
       </c>
       <c r="C2" t="n">
-        <v>0.578717680992443</v>
+        <v>0.5599993183393231</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7839669903453134</v>
+        <v>0.7567206141457</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4234765110873748</v>
+        <v>0.4382359379082863</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7125515522191569</v>
+        <v>0.7087222934321332</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9996491564954054</v>
+        <v>0.9995270032303143</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998526421199809</v>
+        <v>0.9997743984531083</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7469565217391304</v>
+        <v>0.7243478260869565</v>
       </c>
     </row>
   </sheetData>
